--- a/Howelsen_Hill/Refrapy/group3_howelsen_hill_first_picks/gps/group3_topography_data.xlsx
+++ b/Howelsen_Hill/Refrapy/group3_howelsen_hill_first_picks/gps/group3_topography_data.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{891AAE48-7697-4D50-8B26-77CE5C9E235D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3705" yWindow="15" windowWidth="13380" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
